--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/6543-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/6543-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C62A596F-E554-4D21-B0E2-CE73AEE33723}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3CE16ABC-34CA-433B-98AF-D7126F37A210}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{5D28721D-DF99-4962-9979-EC34EEA00247}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{AC089F3A-AB90-4AB5-9CC4-1950E52EA5D3}"/>
   </bookViews>
   <sheets>
     <sheet name="6543-dividend-20260215_1_2" sheetId="1" r:id="rId1"/>
@@ -1463,30 +1463,30 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52657C01-6AC3-4EC5-B0B2-55EAA2358E91}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7D0A996-1E58-4012-BEFE-C026A1ADC997}">
   <dimension ref="A1:X20"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="4" width="7.125" customWidth="1"/>
-    <col min="5" max="5" width="6.75" customWidth="1"/>
-    <col min="6" max="6" width="7.125" customWidth="1"/>
-    <col min="7" max="7" width="6.75" customWidth="1"/>
-    <col min="8" max="10" width="7.125" customWidth="1"/>
-    <col min="11" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="14" width="7.125" customWidth="1"/>
-    <col min="15" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="7.125" customWidth="1"/>
-    <col min="20" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="7.125" customWidth="1"/>
-    <col min="22" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="23" width="7.125" customWidth="1"/>
-    <col min="24" max="24" width="8.625" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="4" width="6.109375" customWidth="1"/>
+    <col min="5" max="5" width="5.88671875" customWidth="1"/>
+    <col min="6" max="6" width="6.109375" customWidth="1"/>
+    <col min="7" max="7" width="5.88671875" customWidth="1"/>
+    <col min="8" max="10" width="6.109375" customWidth="1"/>
+    <col min="11" max="13" width="5.88671875" customWidth="1"/>
+    <col min="14" max="14" width="6.109375" customWidth="1"/>
+    <col min="15" max="18" width="5.88671875" customWidth="1"/>
+    <col min="19" max="19" width="6.109375" customWidth="1"/>
+    <col min="20" max="20" width="5.88671875" customWidth="1"/>
+    <col min="21" max="21" width="6.109375" customWidth="1"/>
+    <col min="22" max="22" width="5.88671875" customWidth="1"/>
+    <col min="23" max="23" width="6.109375" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
@@ -1520,7 +1520,7 @@
       <c r="W1" s="29"/>
       <c r="X1" s="21"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="22" t="s">
         <v>1</v>
       </c>
@@ -1556,7 +1556,7 @@
       <c r="W2" s="31"/>
       <c r="X2" s="32"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="22" t="s">
         <v>2</v>
       </c>
@@ -1608,7 +1608,7 @@
       </c>
       <c r="X3" s="35"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="24"/>
       <c r="B4" s="25"/>
       <c r="C4" s="7"/>
@@ -1676,7 +1676,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="36">
         <v>2025</v>
       </c>
@@ -1748,7 +1748,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
         <v>29</v>
       </c>
@@ -1822,7 +1822,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="38">
         <v>2024</v>
       </c>
@@ -1894,7 +1894,7 @@
         <v>7.55</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="16" t="s">
         <v>29</v>
       </c>
@@ -1968,7 +1968,7 @@
         <v>3.82</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="16" t="s">
         <v>29</v>
       </c>
@@ -2042,7 +2042,7 @@
         <v>3.74</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="36">
         <v>2023</v>
       </c>
@@ -2114,7 +2114,7 @@
         <v>3.6</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="38">
         <v>2022</v>
       </c>
@@ -2186,7 +2186,7 @@
         <v>2.39</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="36">
         <v>2021</v>
       </c>
@@ -2258,7 +2258,7 @@
         <v>4.5199999999999996</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="38">
         <v>2020</v>
       </c>
@@ -2330,7 +2330,7 @@
         <v>7.79</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="36">
         <v>2019</v>
       </c>
@@ -2402,7 +2402,7 @@
         <v>4.26</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="38">
         <v>2018</v>
       </c>
@@ -2474,7 +2474,7 @@
         <v>4.12</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="36">
         <v>2017</v>
       </c>
@@ -2546,7 +2546,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="38">
         <v>2016</v>
       </c>
@@ -2618,7 +2618,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="36">
         <v>2015</v>
       </c>
@@ -2690,7 +2690,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="38">
         <v>2014</v>
       </c>
@@ -2762,7 +2762,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="36" t="s">
         <v>41</v>
       </c>
